--- a/Excel/Smart_Data.xlsx
+++ b/Excel/Smart_Data.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>01:30</t>
         </is>
       </c>
     </row>
@@ -598,12 +598,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>00:30</t>
         </is>
       </c>
     </row>

--- a/Excel/Smart_Data.xlsx
+++ b/Excel/Smart_Data.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Plan" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convert Tour Plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Execution With Presentation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Execution With Presentatio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Execution With Presentation" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,11 +49,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,7 +418,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <cols>
+    <col width="29.90625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="17.36328125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="14.26953125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13.54296875" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -454,12 +461,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-05</t>
         </is>
       </c>
     </row>
@@ -469,6 +476,156 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Appointment Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Appointment Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eddie Davila</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <cols>
+    <col width="23.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="27.54296875" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Convert Plan Contact Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Convert Plan Appointment Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Convert Plan Appointment Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eddie Davila</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <cols>
+    <col width="25.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="29.54296875" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tour Execution Contact Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tour Execution Appointment Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tour Execution Appointment Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eddie Davila</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -480,17 +637,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Contact Name</t>
+          <t>Tour Execution Contact Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Appointment Date</t>
+          <t>Tour Execution Appointment Date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Appointment Time</t>
+          <t>Tour Execution Appointment Time</t>
         </is>
       </c>
     </row>
@@ -502,108 +659,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01:30</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Convert Plan Contact Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Convert Plan Appointment Date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Convert Plan Appointment Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Eddie Davila</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Tour Execution Contact Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Tour Execution Appointment Date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Tour Execution Appointment Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Eddie Davila</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>02:30</t>
         </is>
       </c>
     </row>

--- a/Excel/Smart_Data.xlsx
+++ b/Excel/Smart_Data.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="2" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Plan" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convert Tour Plan" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Execution With Presentatio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Execution With Presentation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recovered_Sheet1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Execution With Presentation" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -459,12 +460,12 @@
           <t>Business Discussion</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
@@ -482,7 +483,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <cols>
+    <col width="12.54296875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.26953125" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -509,12 +514,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>01:15</t>
         </is>
       </c>
     </row>
@@ -559,12 +564,14 @@
           <t>Eddie Davila</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>46027</v>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>01:15</t>
         </is>
       </c>
     </row>
@@ -632,6 +639,58 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <cols>
+    <col width="25.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="29.54296875" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tour Execution Contact Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tour Execution Appointment Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tour Execution Appointment Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eddie Davila</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,7 +718,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/Excel/Smart_Data.xlsx
+++ b/Excel/Smart_Data.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="2" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="32280" yWindow="1230" windowWidth="13830" windowHeight="8415" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Plan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convert Tour Plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Execution With Presentatio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recovered_Sheet1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour Execution With Presentation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Event" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tour Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Convert Tour Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tour Execution With Presentatio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recovered_Sheet1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recovered_Sheet2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recovered_Sheet3" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Tour Execution With Presentation" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -50,9 +54,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,12 +427,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
-    <col width="29.90625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="17.36328125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="14.26953125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13.54296875" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="29.88671875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="17.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="14.21875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="13.5546875" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,12 +468,12 @@
           <t>Business Discussion</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
@@ -483,10 +491,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
-    <col width="12.54296875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="16.26953125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="16.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,14 +521,14 @@
           <t>Eddie Davila</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>01:15</t>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>01:30</t>
         </is>
       </c>
     </row>
@@ -535,10 +544,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
-    <col width="23.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="27.54296875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="23.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="27.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="29.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -564,14 +574,14 @@
           <t>Eddie Davila</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>01:15</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>01:30</t>
         </is>
       </c>
     </row>
@@ -587,10 +597,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
-    <col width="25.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="29.54296875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="25.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="29.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -639,10 +649,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
-    <col width="25.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="29.54296875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="25.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="29.5546875" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -685,6 +695,102 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tour Execution Contact Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tour Execution Appointment Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tour Execution Appointment Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eddie Davila</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tour Execution Contact Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tour Execution Appointment Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tour Execution Appointment Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eddie Davila</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -718,7 +824,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/Excel/Smart_Data.xlsx
+++ b/Excel/Smart_Data.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>01:30</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>01:30</t>
         </is>
       </c>
     </row>
